--- a/output/pdf_financials_xlsx/SFD.xlsx
+++ b/output/pdf_financials_xlsx/SFD.xlsx
@@ -43287,7 +43287,7 @@
         </is>
       </c>
       <c r="L331" s="5" t="n">
-        <v>10.540228</v>
+        <v>-10.540228</v>
       </c>
       <c r="M331" s="5" t="n">
         <v>-9.099562000000001</v>

--- a/output/pdf_financials_xlsx/SFD.xlsx
+++ b/output/pdf_financials_xlsx/SFD.xlsx
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.109374</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.234007</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.080633</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009923</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.350431</v>
+        <v>0.459805</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.141291</v>
+        <v>-0.907284</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.405125</v>
+        <v>-2.324492</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.452428</v>
+        <v>-4.442505</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-3.584601</v>
@@ -2294,16 +2294,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.47861</v>
+        <v>0.587984</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.969678</v>
+        <v>-0.735671</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.23154</v>
+        <v>-2.150907</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.452428</v>
+        <v>-4.442505</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.584601</v>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8.483447873439387</v>
+        <v>10.42212159047321</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-32.81413384896831</v>
+        <v>-24.8952813849591</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-60.5685223581103</v>
+        <v>-58.3799791712073</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -8558,19 +8558,19 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>1</v>
+        <v>0.201891</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-0.064815</v>
+        <v>-0.785124</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-0.111111</v>
+        <v>-0.850638</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>-0.111111</v>
+        <v>-0.475823</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>-0.111111</v>
+        <v>-0.351787</v>
       </c>
     </row>
     <row r="125">
@@ -8619,19 +8619,19 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>1</v>
+        <v>0.201891</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-0.064815</v>
+        <v>-0.785124</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-0.111111</v>
+        <v>-0.850638</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>-0.111111</v>
+        <v>-0.475823</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>-0.111111</v>
+        <v>-0.351787</v>
       </c>
     </row>
     <row r="126">
@@ -23314,7 +23314,11 @@
           <t>Lease payments (Note 13)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -27688,7 +27692,11 @@
           <t>Lease payments (Note 12)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -29818,7 +29826,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -61850,7 +61862,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -63304,7 +63316,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E526" s="5" t="n">

--- a/output/pdf_financials_xlsx/SFD.xlsx
+++ b/output/pdf_financials_xlsx/SFD.xlsx
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.050239</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -47786,7 +47786,11 @@
           <t>Issue of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SFD.xlsx
+++ b/output/pdf_financials_xlsx/SFD.xlsx
@@ -2254,19 +2254,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.704943</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>2.104864</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>1.897576</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>1.790267</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.781181</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         <v>-4.942015</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.688136</v>
+        <v>6.393079</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-8.725051000000001</v>
+        <v>-6.620187</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.894852999999999</v>
+        <v>-6.997277</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.968511</v>
+        <v>-5.178244</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>3.772908</v>
+        <v>5.554089</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-6.028228</v>
@@ -3043,28 +3043,28 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.061279</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.086523</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.161489</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.035107</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.057065</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.08982900000000001</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.083648</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>0.09665</v>
       </c>
     </row>
     <row r="41">
@@ -3110,28 +3110,28 @@
         <v>0.060027</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.061279</v>
+        <v>0.122558</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.709015</v>
+        <v>1.795538</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0.965548</v>
+        <v>1.127037</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0.841567</v>
+        <v>0.876674</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.057065</v>
+        <v>0.11413</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>1.828523</v>
+        <v>1.918352</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0.105858</v>
+        <v>0.189506</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.92884</v>
+        <v>3.02549</v>
       </c>
     </row>
     <row r="42">
@@ -3579,28 +3579,28 @@
         <v>0.107363</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.06515899999999999</v>
+        <v>0.00388</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.097132</v>
+        <v>0.010609</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.077532</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.265436</v>
+        <v>0.230329</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.036157</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.053673</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.274799</v>
+        <v>0.191151</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.520293</v>
+        <v>1.423643</v>
       </c>
     </row>
     <row r="49">
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>2.286121</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>2.371605</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
@@ -5095,28 +5095,28 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.042603</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.736408</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.773465</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.532936</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.650315</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.343513</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.693607</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>0.752378</v>
       </c>
     </row>
     <row r="71">
@@ -5162,28 +5162,28 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.042603</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.736408</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.773465</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.064815</v>
+        <v>0.597751</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.111111</v>
+        <v>0.761426</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.111111</v>
+        <v>0.454624</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.111111</v>
+        <v>0.804718</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.111111</v>
+        <v>0.863489</v>
       </c>
     </row>
     <row r="72">
@@ -5430,28 +5430,28 @@
         <v>0.03978</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.042603</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.867794</v>
+        <v>0.131386</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.900972</v>
+        <v>0.127507</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.532936</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.650315</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.186079</v>
+        <v>1.842566</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>5.608855</v>
+        <v>4.915248</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>1.339169</v>
+        <v>0.586791</v>
       </c>
     </row>
     <row r="76">
@@ -5778,35 +5778,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.001721082507288736</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.02629866646782177</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.03501407122342799</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.05192868052702002</v>
+        <v>0.07960334381236797</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.06618324007116935</v>
+        <v>0.1122061700442576</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.06499344603110256</v>
+        <v>0.09208578679962837</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.09465730683463877</v>
+        <v>0.1867447933124129</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>0.03347917972972432</v>
+        <v>0.07533165888853832</v>
       </c>
     </row>
     <row r="81">
@@ -7062,19 +7056,19 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.704943</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>2.104864</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.897576</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.790267</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.781181</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -7992,13 +7986,13 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>3.436691</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>-0.208739</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -9239,10 +9233,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>3.85185</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-1.81615</v>
@@ -9253,20 +9245,14 @@
       <c r="E135" s="3" t="n">
         <v>-2.692776</v>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>-1.79549</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0.744439</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>-0.795421</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>6.984922</v>
@@ -11050,7 +11036,11 @@
           <t>Current portion of lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -13054,7 +13044,11 @@
           <t>Current portion of lease obligations (Note 12)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -15888,7 +15882,11 @@
           <t>Current portion of lease obligation (Note 13)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -24016,7 +24014,11 @@
           <t>Net proceeds from Private Placement (Note 16)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25296,7 +25298,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -28310,7 +28316,11 @@
           <t>Net proceeds from Private Placement (Note 15)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -28622,7 +28632,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -29118,7 +29132,11 @@
           <t>Private placements (Note 15)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -30460,7 +30478,11 @@
           <t>Proceeds from (used in) short-term investments</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -32010,7 +32032,11 @@
           <t>Private placement (Note 15) $</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -32602,7 +32628,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E228" s="5" t="n">
         <v>0.350431</v>
       </c>
@@ -33520,7 +33550,11 @@
           <t>Net proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -34130,7 +34164,11 @@
           <t>Issuance of common stock on Private Placement</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -34542,7 +34580,11 @@
           <t>Issuance of warrants on Private Placement (Note 15)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -35054,7 +35096,11 @@
           <t>Amortization expense (Notes 8 &amp; 9)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -36106,7 +36152,11 @@
           <t>Net Proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -36934,7 +36984,11 @@
           <t>Issuance of Common Stock on Private Placement (Note 15)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -38468,7 +38522,11 @@
           <t>Amortization expense (Notes 5 &amp; 6)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -39404,7 +39462,11 @@
           <t>Net Proceeds from Private Placement (Note 10)</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -40024,7 +40086,11 @@
           <t>Issuance of Common Stock on Private Placement (Note 10)</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -40654,7 +40720,11 @@
           <t>Issuance of warrants on Private Placement (Note 10 and 21)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -41280,7 +41350,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -41492,7 +41566,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -44078,7 +44156,11 @@
           <t>Net cash generated by (used in) operating activities</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -51404,7 +51486,11 @@
           <t>Net cash generated (used) in operating activities</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E410" s="5" t="n">
         <v>3.85185</v>
       </c>
@@ -56906,7 +56992,11 @@
           <t>Amortization expense (Notes 7 &amp; 8)</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -57738,7 +57828,11 @@
           <t>Amortization expense (Notes 5 &amp; 6)</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -58778,7 +58872,11 @@
           <t>Amortization expense (Note 4)</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -59300,7 +59398,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
